--- a/AJA/Kavya/backend/Output/PJPA28_Generated.xlsx
+++ b/AJA/Kavya/backend/Output/PJPA28_Generated.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Anomalies (30-32)" sheetId="1" r:id="rId1"/>
+    <sheet name="Anomalies" sheetId="1" r:id="rId1"/>
     <sheet name="Summary Stats" sheetId="2" r:id="rId2"/>
     <sheet name="1st Digit Analysis" sheetId="3" r:id="rId3"/>
     <sheet name="2nd Digit Analysis" sheetId="4" r:id="rId4"/>
@@ -7622,7 +7622,7 @@
     <t>Local Conveyance (Within City)</t>
   </si>
   <si>
-    <t>Presents a high-level overview of the analysis results, including sample sizes, Mean Absolute Deviation (MAD), and critical findings for each test type.</t>
+    <t>Summary Overview</t>
   </si>
   <si>
     <t>Analysis Type</t>
@@ -7658,7 +7658,7 @@
     <t>Z-Score Max: 20.59 (Pair 30)</t>
   </si>
   <si>
-    <t>Compares the actual count of leading digits (1–9) with the expected Benford's Law distribution to detect potential irregularities.</t>
+    <t>1st Digit Analysis</t>
   </si>
   <si>
     <t>Digit</t>
@@ -7685,10 +7685,10 @@
     <t>Z-Score</t>
   </si>
   <si>
-    <t>Analyzes the distribution of the second digit (0–9) in the dataset against the theoretical expectations of Benford's Law.</t>
-  </si>
-  <si>
-    <t>Provides a statistical comparison of the actual vs. expected frequency for the first two digits (10–99), including Z-scores to identify deviations.</t>
+    <t>2nd Digit Analysis</t>
+  </si>
+  <si>
+    <t>First-2 Digits Analysis</t>
   </si>
 </sst>
 </file>
